--- a/Shared/XLS/Projectile.xlsx
+++ b/Shared/XLS/Projectile.xlsx
@@ -303,18 +303,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>PJT_CrossBow_Bolt</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_CrossBow_Attack_Damage</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefab_Projectile_CrossBow_Bolt</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>PJT_Monster_Arrow</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -324,6 +312,18 @@
   </si>
   <si>
     <t>SE_Monster_RangeAttack_Damage</t>
+  </si>
+  <si>
+    <t>PJT_Pistol_Bullet</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefab_Projectile_Pistol_Bullet</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_Pistol_Attack_Damage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -765,7 +765,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -867,31 +867,31 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B4" s="9" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D4" s="9">
         <v>1</v>
       </c>
       <c r="E4" s="9"/>
       <c r="F4" s="9" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G4" s="9"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B5" s="9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="9" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G5" s="9"/>
     </row>

--- a/Shared/XLS/Projectile.xlsx
+++ b/Shared/XLS/Projectile.xlsx
@@ -314,15 +314,15 @@
     <t>SE_Monster_RangeAttack_Damage</t>
   </si>
   <si>
-    <t>PJT_Pistol_Bullet</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefab_Projectile_Pistol_Bullet</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_Pistol_Attack_Damage</t>
+    <t>PJT_Shuriken_Bullet</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefab_Projectile_Shuriken_Bullet</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_Shuriken_Attack_Damage</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -765,7 +765,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/Shared/XLS/Projectile.xlsx
+++ b/Shared/XLS/Projectile.xlsx
@@ -1,99 +1,184 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240"/>
   </bookViews>
   <sheets>
-    <sheet name="#Projectile" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="#Projectile" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="145621" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>양대용</author>
+  </authors>
+  <commentList>
+    <comment ref="F2" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="맑은 고딕"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>착탄 폭발 반경. 
+0 = 충돌 대상 1체만
+1이상 = 착탄점 반경 내 전원</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
+  <si>
+    <t>!EnumTable</t>
+  </si>
+  <si>
+    <t>Projectile</t>
+  </si>
+  <si>
+    <t>!ID</t>
+  </si>
+  <si>
+    <t>PrefabPath</t>
+  </si>
+  <si>
+    <t>Pierce</t>
+  </si>
+  <si>
+    <t>ExplodeRadius</t>
+  </si>
+  <si>
+    <t>HitEffectID_1</t>
+  </si>
+  <si>
+    <t>HitEffectID_2</t>
+  </si>
+  <si>
+    <t>!Projectile</t>
+  </si>
+  <si>
+    <t>!string</t>
+  </si>
+  <si>
+    <t>!int</t>
+  </si>
+  <si>
+    <t>!float</t>
+  </si>
+  <si>
+    <t>!SkillEffect</t>
+  </si>
+  <si>
+    <t>PJT_Shuriken_Bullet</t>
+  </si>
+  <si>
+    <t>SE_Shuriken_Attack_Damage</t>
+  </si>
+  <si>
+    <t>PJT_Monster_Arrow</t>
+  </si>
+  <si>
+    <t>Prefab_Projectile_Monster_Arrow</t>
+  </si>
+  <si>
+    <t>SE_Monster_RangeAttack_Damage</t>
+  </si>
+  <si>
+    <t>PJT_Rifle_Bullet</t>
+  </si>
+  <si>
+    <t>Prefab_Projectile_Rifle_Bullet</t>
+  </si>
+  <si>
+    <t>SE_Rifle_Attack_Damage</t>
+  </si>
+  <si>
+    <t>Bounce</t>
+  </si>
+  <si>
+    <t>Prefab_Projectile_Shuriken</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
+      <family val="2"/>
       <charset val="129"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
+      <family val="2"/>
       <charset val="129"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="8"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <sz val="8"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Tahoma"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color indexed="81"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="돋움"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color indexed="81"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.1499984740745262"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.5999938962981048"/>
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -148,131 +233,52 @@
     </border>
   </borders>
   <cellStyleXfs count="3">
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
+    <cellStyle name="40% - 강조색3" xfId="1" builtinId="39"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="40% - 강조색3" xfId="1" builtinId="39"/>
     <cellStyle name="표준 2" xfId="2"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>양대용</author>
-  </authors>
-  <commentList>
-    <comment ref="E2" authorId="0" shapeId="0">
-      <text>
-        <t>착탄 폭발 반경. 
-0 = 충돌 대상 1체만
-1이상 = 착탄점 반경 내 전원</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -530,201 +536,161 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:O9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:P6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="11.625" bestFit="1" customWidth="1" style="5" min="1" max="1"/>
-    <col width="18" bestFit="1" customWidth="1" style="10" min="2" max="2"/>
-    <col width="30.625" bestFit="1" customWidth="1" style="10" min="3" max="3"/>
-    <col width="6.625" bestFit="1" customWidth="1" style="10" min="4" max="4"/>
-    <col width="14.25" bestFit="1" customWidth="1" style="10" min="5" max="5"/>
-    <col width="32.875" bestFit="1" customWidth="1" style="10" min="6" max="6"/>
-    <col width="18" customWidth="1" style="10" min="7" max="7"/>
-    <col width="9" customWidth="1" style="10" min="8" max="8"/>
+    <col min="1" max="1" width="11.625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.625" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.625" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.625" style="10" customWidth="1"/>
+    <col min="6" max="6" width="14.25" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="32.875" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18" style="10" customWidth="1"/>
+    <col min="9" max="9" width="9" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>!EnumTable</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>Projectile</t>
-        </is>
-      </c>
-      <c r="C1" s="8" t="n"/>
-      <c r="D1" s="8" t="n"/>
-      <c r="E1" s="8" t="n"/>
-      <c r="F1" s="8" t="n"/>
-      <c r="G1" s="8" t="n"/>
-      <c r="H1" s="8" t="n"/>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="n"/>
-      <c r="L1" s="1" t="n"/>
-      <c r="M1" s="1" t="n"/>
-      <c r="N1" s="1" t="n"/>
-      <c r="O1" s="1" t="n"/>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
     </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>!ID</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>PrefabPath</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Pierce</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>ExplodeRadius</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>HitEffectID_1</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>HitEffectID_2</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
-      <c r="L2" s="2" t="n"/>
-      <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n"/>
-      <c r="O2" s="2" t="n"/>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2" s="4"/>
+      <c r="B2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="3"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>!Projectile</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>!string</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>!int</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>!float</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>!SkillEffect</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>!SkillEffect</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
-      <c r="O3" s="2" t="n"/>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3" s="4"/>
+      <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="3"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
     </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>PJT_Shuriken_Bullet</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Prefab_Projectile_Shuriken_Bullet</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="9">
         <v>1</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>SE_Shuriken_Attack_Damage</t>
-        </is>
+      <c r="G4" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>PJT_Monster_Arrow</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Prefab_Projectile_Monster_Arrow</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>SE_Monster_RangeAttack_Damage</t>
-        </is>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>PJT_Rifle_Bullet</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Prefab_Projectile_Rifle_Bullet</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6">
         <v>99</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SE_Rifle_Attack_Damage</t>
-        </is>
+      <c r="E6" s="9"/>
+      <c r="G6" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>